--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41E6AFC-F9D3-48BC-982C-F712638428A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4780C82F-97CF-4420-83B2-F87823CB6C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Voice lines" sheetId="1" r:id="rId1"/>
+    <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="132">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -86,9 +86,6 @@
     <t>fire extinguisher</t>
   </si>
   <si>
-    <t>clothesline</t>
-  </si>
-  <si>
     <t>hamster</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t>wels</t>
   </si>
   <si>
-    <t>shrimp</t>
-  </si>
-  <si>
     <t>hmm a snäcc</t>
   </si>
   <si>
@@ -185,36 +179,18 @@
     <t>person 5</t>
   </si>
   <si>
-    <t>person 6</t>
-  </si>
-  <si>
     <t>person 7</t>
   </si>
   <si>
-    <t>shirt</t>
-  </si>
-  <si>
     <t>cloak</t>
   </si>
   <si>
-    <t>trousers</t>
-  </si>
-  <si>
     <t>underwear</t>
   </si>
   <si>
-    <t>jacket</t>
-  </si>
-  <si>
     <t>goose</t>
   </si>
   <si>
-    <t>dress</t>
-  </si>
-  <si>
-    <t>blanket</t>
-  </si>
-  <si>
     <t>Wizard</t>
   </si>
   <si>
@@ -233,9 +209,6 @@
     <t>ugh i really don't like making phone calls</t>
   </si>
   <si>
-    <t>where did that come from?</t>
-  </si>
-  <si>
     <t>damn i'm hungry right now</t>
   </si>
   <si>
@@ -396,6 +369,69 @@
   </si>
   <si>
     <t>Inventory?</t>
+  </si>
+  <si>
+    <t>books</t>
+  </si>
+  <si>
+    <t>rope</t>
+  </si>
+  <si>
+    <t>hide the pain harold</t>
+  </si>
+  <si>
+    <t>You look comfy</t>
+  </si>
+  <si>
+    <t>he seems busy / are you winning son?</t>
+  </si>
+  <si>
+    <t>you look bored?</t>
+  </si>
+  <si>
+    <t>ah those plants really needed watering / here you go</t>
+  </si>
+  <si>
+    <t>there's something in there /there's nothing in there</t>
+  </si>
+  <si>
+    <t>it's a desk</t>
+  </si>
+  <si>
+    <t>i already have one of these</t>
+  </si>
+  <si>
+    <t>i think i'm just gonna take them all</t>
+  </si>
+  <si>
+    <t>it's a couch table</t>
+  </si>
+  <si>
+    <t>mermaid statue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t>i could put it up somewhere</t>
+  </si>
+  <si>
+    <t>they looked very hydrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you like the vertically rotating fish? </t>
+  </si>
+  <si>
+    <t>oh vertically rotating fish</t>
+  </si>
+  <si>
+    <t>why do you have to be such an asshole?</t>
+  </si>
+  <si>
+    <t>it's a permanent marker</t>
+  </si>
+  <si>
+    <t>where did that come from? … hmm</t>
   </si>
 </sst>
 </file>
@@ -796,261 +832,261 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99E062-B379-4255-9A7C-7981EB663D4D}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="4" max="4" width="38.77734375" customWidth="1"/>
-    <col min="5" max="5" width="46.5546875" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="3" max="3" width="42.77734375" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="56.44140625" customWidth="1"/>
+    <col min="6" max="6" width="41.6640625" customWidth="1"/>
     <col min="7" max="7" width="49.44140625" customWidth="1"/>
-    <col min="8" max="8" width="32.5546875" customWidth="1"/>
-    <col min="9" max="9" width="28.109375" customWidth="1"/>
+    <col min="8" max="8" width="46.33203125" customWidth="1"/>
+    <col min="9" max="9" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
+      <c r="C5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" t="s">
-        <v>79</v>
+      <c r="C6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" t="s">
-        <v>63</v>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -1058,116 +1094,119 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>33</v>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" t="s">
-        <v>76</v>
+      <c r="C12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -1175,7 +1214,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
@@ -1183,630 +1222,835 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" t="s">
-        <v>35</v>
+      <c r="C20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I24" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" t="s">
-        <v>27</v>
+        <v>109</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>31</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
+        <v>108</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" t="s">
         <v>36</v>
       </c>
-      <c r="C29" t="s">
-        <v>115</v>
-      </c>
-      <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29" t="s">
-        <v>37</v>
-      </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
         <v>43</v>
       </c>
-      <c r="C30" t="s">
-        <v>45</v>
-      </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
+        <v>109</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" t="s">
-        <v>51</v>
+        <v>26</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
+        <v>109</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
+        <v>109</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" t="s">
-        <v>53</v>
+        <v>26</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" t="s">
-        <v>60</v>
+        <v>109</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" t="s">
-        <v>48</v>
+        <v>109</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" t="s">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" t="s">
-        <v>49</v>
+        <v>109</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s">
-        <v>57</v>
+        <v>26</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" t="s">
-        <v>50</v>
+        <v>109</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s">
-        <v>58</v>
+        <v>26</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
+        <v>78</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" t="s">
-        <v>92</v>
-      </c>
-      <c r="E41" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" t="s">
-        <v>96</v>
-      </c>
-      <c r="H41" t="s">
-        <v>94</v>
-      </c>
-      <c r="I41" t="s">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>116</v>
+        <v>107</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4780C82F-97CF-4420-83B2-F87823CB6C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5467B16-1592-4723-B63B-00751DC2E9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="133">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -278,9 +278,6 @@
     <t>poster</t>
   </si>
   <si>
-    <t>something missing</t>
-  </si>
-  <si>
     <t>bees?</t>
   </si>
   <si>
@@ -432,6 +429,12 @@
   </si>
   <si>
     <t>where did that come from? … hmm</t>
+  </si>
+  <si>
+    <t>hehe</t>
+  </si>
+  <si>
+    <t>something is missing here</t>
   </si>
 </sst>
 </file>
@@ -461,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,6 +483,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -493,11 +502,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -847,17 +857,17 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -883,7 +893,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -912,65 +922,65 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="F5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -999,94 +1009,94 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="E7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="C9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -1094,7 +1104,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -1123,7 +1133,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
@@ -1152,7 +1162,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -1181,7 +1191,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
@@ -1195,7 +1205,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
@@ -1206,7 +1216,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -1214,7 +1224,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
@@ -1222,7 +1232,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>14</v>
@@ -1245,103 +1255,103 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="E21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
         <v>94</v>
       </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
         <v>61</v>
@@ -1349,7 +1359,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>16</v>
@@ -1361,7 +1371,7 @@
         <v>26</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>26</v>
@@ -1378,7 +1388,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>17</v>
@@ -1407,36 +1417,36 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="D25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -1448,7 +1458,7 @@
         <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>26</v>
@@ -1465,36 +1475,36 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="E27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>33</v>
@@ -1503,42 +1513,42 @@
         <v>26</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
         <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
         <v>36</v>
@@ -1549,7 +1559,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>41</v>
@@ -1563,7 +1573,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>44</v>
@@ -1572,7 +1582,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
@@ -1592,7 +1602,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>51</v>
@@ -1621,7 +1631,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>45</v>
@@ -1630,7 +1640,7 @@
         <v>26</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -1650,7 +1660,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>52</v>
@@ -1679,7 +1689,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>46</v>
@@ -1688,7 +1698,7 @@
         <v>26</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
         <v>26</v>
@@ -1708,16 +1718,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
         <v>26</v>
@@ -1737,7 +1747,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>47</v>
@@ -1746,7 +1756,7 @@
         <v>26</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -1766,32 +1776,35 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="C38" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -1806,7 +1819,7 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="G40" t="s">
         <v>79</v>
@@ -1820,195 +1833,195 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>122</v>
+        <v>90</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>119</v>
+        <v>95</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
         <v>98</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>119</v>
+        <v>101</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -2016,41 +2029,41 @@
         <v>66</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5467B16-1592-4723-B63B-00751DC2E9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6970E3-88EE-4DB5-B0EA-7CE5116BD903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="133">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -1364,25 +1364,25 @@
       <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="C23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="F23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1393,25 +1393,25 @@
       <c r="B24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="C24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="1" t="s">
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1509,25 +1509,25 @@
       <c r="B28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="4" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1787,18 +1787,30 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="D39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1838,25 +1850,25 @@
       <c r="B41" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="4" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2024,33 +2036,36 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>123</v>
       </c>
@@ -2058,7 +2073,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>107</v>
       </c>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6970E3-88EE-4DB5-B0EA-7CE5116BD903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB443F79-4A7E-4FB5-A016-6BF65AA2D75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="135">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -435,6 +435,12 @@
   </si>
   <si>
     <t>something is missing here</t>
+  </si>
+  <si>
+    <t>aur naur cleo</t>
+  </si>
+  <si>
+    <t>classic selection</t>
   </si>
 </sst>
 </file>
@@ -464,7 +470,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +495,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -502,12 +514,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -892,7 +906,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -921,7 +935,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -956,54 +970,54 @@
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="G5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1014,25 +1028,25 @@
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="E7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1043,25 +1057,25 @@
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1138,25 +1152,25 @@
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1254,7 +1268,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1283,60 +1297,60 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="E21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1358,7 +1372,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1387,7 +1401,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1416,31 +1430,31 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1451,25 +1465,25 @@
       <c r="B26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="C26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="F26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1480,25 +1494,25 @@
       <c r="B27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="4" t="s">
+      <c r="E27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1509,25 +1523,25 @@
       <c r="B28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="C28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1538,24 +1552,25 @@
       <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1581,7 +1596,7 @@
       <c r="C31" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="4" t="s">
         <v>126</v>
       </c>
       <c r="E31" t="s">
@@ -1639,7 +1654,7 @@
       <c r="C33" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E33" t="s">
@@ -1697,7 +1712,7 @@
       <c r="C35" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="4" t="s">
         <v>115</v>
       </c>
       <c r="E35" t="s">
@@ -1775,7 +1790,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -1887,25 +1902,25 @@
       <c r="B43" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="6" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1916,25 +1931,25 @@
       <c r="B44" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="6" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1956,25 +1971,25 @@
       <c r="B46" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="6" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1985,25 +2000,25 @@
       <c r="B47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="6" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2014,31 +2029,31 @@
       <c r="B48" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>66</v>
+      <c r="A49" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>106</v>
@@ -2066,11 +2081,14 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="4" t="s">
         <v>123</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>110</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
@@ -2079,6 +2097,27 @@
       </c>
       <c r="B51" s="1" t="s">
         <v>122</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB443F79-4A7E-4FB5-A016-6BF65AA2D75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54FACD0-CB7A-41CD-92A6-DD801CCDBA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
     <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>
+    <sheet name="Voice lines interaction" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="144">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -441,6 +442,33 @@
   </si>
   <si>
     <t>classic selection</t>
+  </si>
+  <si>
+    <t>mermaid</t>
+  </si>
+  <si>
+    <t>obviously</t>
+  </si>
+  <si>
+    <t>i think there's a future for me in interior design</t>
+  </si>
+  <si>
+    <t>you know what… it does make sense somehow</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>hell yeah</t>
+  </si>
+  <si>
+    <t>yeah</t>
+  </si>
+  <si>
+    <t>here you go</t>
+  </si>
+  <si>
+    <t>hehe way better now</t>
   </si>
 </sst>
 </file>
@@ -470,7 +498,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,6 +529,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -514,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -522,6 +562,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2124,4 +2173,366 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A1D417-ADA9-469E-98A7-71A705D892D3}">
+  <dimension ref="A1:T51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="11.5546875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="N2" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="P19" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" s="8"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" s="8"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P27" s="8"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q37" s="8"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R48" s="8"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="S49" s="8"/>
+    </row>
+    <row r="50" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="T50" s="8"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54FACD0-CB7A-41CD-92A6-DD801CCDBA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4B19DC-4617-4D74-8B06-A1FE40BFC5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
     <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="149">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -469,6 +469,21 @@
   </si>
   <si>
     <t>hehe way better now</t>
+  </si>
+  <si>
+    <t>can i interest you in a book?</t>
+  </si>
+  <si>
+    <t>it's already perfect</t>
+  </si>
+  <si>
+    <t>that would be animal cruelty</t>
+  </si>
+  <si>
+    <t>it's been through enough already</t>
+  </si>
+  <si>
+    <t>maybe? Ouch it bit me</t>
   </si>
 </sst>
 </file>
@@ -554,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -571,6 +586,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1819,7 +1835,7 @@
       <c r="C37" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="10" t="s">
         <v>113</v>
       </c>
       <c r="E37" t="s">
@@ -2262,6 +2278,9 @@
         <v>1</v>
       </c>
       <c r="D4" s="8"/>
+      <c r="P4" s="9" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -2330,18 +2349,18 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>15</v>
       </c>
@@ -2350,58 +2369,91 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>111</v>
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>16</v>
       </c>
+      <c r="B22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="L22" s="8"/>
-    </row>
-    <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="P22" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>17</v>
       </c>
       <c r="M23" s="8"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>31</v>
       </c>
       <c r="O26" s="8"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="D27" s="9" t="s">
+        <v>145</v>
+      </c>
       <c r="P27" s="8"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
@@ -2409,17 +2461,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>45</v>
       </c>
@@ -2427,38 +2479,41 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S34" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>77</v>
       </c>
       <c r="Q37" s="8"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>28</v>
       </c>
@@ -2466,47 +2521,47 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>106</v>
       </c>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4B19DC-4617-4D74-8B06-A1FE40BFC5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A566E5-8651-4EB4-BC55-196E65189153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
     <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="152">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -183,9 +183,6 @@
     <t>person 7</t>
   </si>
   <si>
-    <t>cloak</t>
-  </si>
-  <si>
     <t>underwear</t>
   </si>
   <si>
@@ -252,9 +249,6 @@
     <t>it's vacuum cleaner</t>
   </si>
   <si>
-    <t>now it's not comfy anymore</t>
-  </si>
-  <si>
     <t>that's it, i'm calling the police</t>
   </si>
   <si>
@@ -484,6 +478,21 @@
   </si>
   <si>
     <t>maybe? Ouch it bit me</t>
+  </si>
+  <si>
+    <t>do your best, be a gay wizard</t>
+  </si>
+  <si>
+    <t>pondering</t>
+  </si>
+  <si>
+    <t>teach man fish</t>
+  </si>
+  <si>
+    <t>Not my favourite anime.</t>
+  </si>
+  <si>
+    <t>couch</t>
   </si>
 </sst>
 </file>
@@ -569,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -586,7 +595,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -921,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99E062-B379-4255-9A7C-7981EB663D4D}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -936,17 +944,17 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -972,36 +980,36 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="D3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -1030,22 +1038,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>26</v>
@@ -1059,45 +1067,45 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>26</v>
@@ -1117,65 +1125,65 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -1183,492 +1191,555 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" t="s">
-        <v>71</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>106</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>108</v>
+      <c r="A15" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
+        <v>98</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
+      <c r="A16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>107</v>
+      <c r="A17" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>13</v>
+        <v>109</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s">
-        <v>76</v>
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>75</v>
+      <c r="A19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>15</v>
+      <c r="A20" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="G25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>129</v>
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>105</v>
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>26</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I29" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>26</v>
+      </c>
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
         <v>26</v>
@@ -1682,22 +1753,22 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
       </c>
-      <c r="D32" t="s">
-        <v>48</v>
+      <c r="D32" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G32" t="s">
         <v>26</v>
@@ -1711,22 +1782,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
         <v>26</v>
@@ -1739,450 +1810,341 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>108</v>
+      <c r="A34" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" t="s">
-        <v>26</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" t="s">
-        <v>26</v>
+        <v>76</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" t="s">
-        <v>26</v>
+        <v>123</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>114</v>
+        <v>28</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" t="s">
-        <v>26</v>
+        <v>77</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" t="s">
-        <v>26</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" t="s">
-        <v>26</v>
-      </c>
-      <c r="I37" t="s">
-        <v>26</v>
+        <v>97</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>107</v>
+      <c r="A38" t="s">
+        <v>106</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>131</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>125</v>
+      <c r="C39" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" t="s">
-        <v>79</v>
-      </c>
-      <c r="E40" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" t="s">
-        <v>132</v>
-      </c>
-      <c r="G40" t="s">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s">
-        <v>79</v>
-      </c>
-      <c r="I40" t="s">
-        <v>79</v>
+        <v>93</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>108</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>118</v>
+      <c r="C46" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H49" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>107</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>133</v>
+      <c r="C47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2222,13 +2184,13 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>16</v>
@@ -2246,16 +2208,16 @@
         <v>33</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -2264,7 +2226,7 @@
       </c>
       <c r="B2" s="8"/>
       <c r="N2" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -2279,7 +2241,7 @@
       </c>
       <c r="D4" s="8"/>
       <c r="P4" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -2319,7 +2281,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
@@ -2356,7 +2318,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I18" s="8"/>
     </row>
@@ -2366,18 +2328,18 @@
       </c>
       <c r="J19" s="8"/>
       <c r="P19" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K20" s="8"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
@@ -2385,35 +2347,35 @@
         <v>16</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L22" s="8"/>
       <c r="P22" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -2444,7 +2406,7 @@
         <v>33</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P27" s="8"/>
     </row>
@@ -2458,7 +2420,7 @@
         <v>41</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -2468,7 +2430,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
@@ -2476,12 +2438,12 @@
         <v>45</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2489,12 +2451,12 @@
         <v>46</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -2504,13 +2466,13 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2518,73 +2480,73 @@
         <v>28</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R48" s="8"/>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S49" s="8"/>
     </row>
     <row r="50" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="T50" s="8"/>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A566E5-8651-4EB4-BC55-196E65189153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D93D92-DA19-4779-BA37-33182350E349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
     <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="154">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -57,30 +57,15 @@
     <t>fridge with freezer</t>
   </si>
   <si>
-    <t>Super Nintendo</t>
-  </si>
-  <si>
     <t>microphone</t>
   </si>
   <si>
-    <t>cushions</t>
-  </si>
-  <si>
     <t>couch with cushions</t>
   </si>
   <si>
-    <t>couch without cushions</t>
-  </si>
-  <si>
     <t>pc with keyboard</t>
   </si>
   <si>
-    <t>pc without keyboard</t>
-  </si>
-  <si>
-    <t>keyboard</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
@@ -493,6 +478,27 @@
   </si>
   <si>
     <t>couch</t>
+  </si>
+  <si>
+    <t>I have the hamster what now?</t>
+  </si>
+  <si>
+    <t>It's still frozen.</t>
+  </si>
+  <si>
+    <t>paywall</t>
+  </si>
+  <si>
+    <t>Ralf Schumacher</t>
+  </si>
+  <si>
+    <t>Robert Pattinson</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>not frozen</t>
   </si>
 </sst>
 </file>
@@ -561,7 +567,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,15 +590,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -944,319 +952,319 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>26</v>
+      <c r="C3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>26</v>
+      <c r="C5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>26</v>
+      <c r="C7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>54</v>
+      <c r="C8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>26</v>
+      <c r="C9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>66</v>
+        <v>146</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1266,653 +1274,688 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" t="s">
-        <v>74</v>
+        <v>9</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>105</v>
+      <c r="A15" t="s">
+        <v>100</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>105</v>
+      <c r="A16" t="s">
+        <v>100</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>26</v>
+      <c r="C23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>127</v>
+        <v>28</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" t="s">
-        <v>42</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" t="s">
-        <v>129</v>
+        <v>70</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I36" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>83</v>
+      <c r="H37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -1924,227 +1967,239 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>119</v>
+        <v>83</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>116</v>
+        <v>88</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" t="s">
-        <v>96</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>116</v>
+        <v>94</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>116</v>
+        <v>95</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>115</v>
+        <v>97</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>132</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2155,398 +2210,374 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A1D417-ADA9-469E-98A7-71A705D892D3}">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="11.5546875" style="7"/>
+    <col min="1" max="16384" width="11.5546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="L2" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R1" s="7" t="s">
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="N15" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="S1" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T1" s="7" t="s">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="N18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="P44" s="7"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q45" s="7"/>
+    </row>
+    <row r="46" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="R46" s="7"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="N2" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="P4" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="P19" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="L22" s="8"/>
-      <c r="P22" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="O26" s="8"/>
-    </row>
-    <row r="27" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P27" s="8"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S34" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q37" s="8"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="R48" s="8"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="S49" s="8"/>
-    </row>
-    <row r="50" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="T50" s="8"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D93D92-DA19-4779-BA37-33182350E349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4BD349-817C-4605-9F13-FD1C1192AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="155">
   <si>
     <t>Piranha Plant</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t>not frozen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pc </t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1263,7 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>154</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
@@ -1905,7 +1908,7 @@
       <c r="D36" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="4" t="s">
         <v>72</v>
       </c>
       <c r="F36" s="4" t="s">
@@ -1917,7 +1920,7 @@
       <c r="H36" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="4" t="s">
         <v>72</v>
       </c>
     </row>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4BD349-817C-4605-9F13-FD1C1192AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
     <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4BD349-817C-4605-9F13-FD1C1192AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D055451C-D729-4DBD-8B93-9A088B29EFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
@@ -570,7 +570,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -600,10 +600,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1025,25 +1026,25 @@
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1083,25 +1084,25 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1265,15 +1266,15 @@
       <c r="B13" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1282,21 +1283,21 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1307,25 +1308,25 @@
       <c r="B15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1365,25 +1366,25 @@
       <c r="B17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
+      <c r="E17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1394,25 +1395,25 @@
       <c r="B18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
@@ -1508,25 +1509,25 @@
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="C22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
+      <c r="F22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1595,25 +1596,25 @@
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="4"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1622,17 +1623,17 @@
       <c r="B26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1644,13 +1645,13 @@
       <c r="C27" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>119</v>
       </c>
       <c r="E27" t="s">
         <v>21</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G27" t="s">
@@ -1673,13 +1674,13 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>143</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G28" t="s">
@@ -1702,13 +1703,13 @@
       <c r="C29" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>21</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G29" t="s">
@@ -1731,13 +1732,13 @@
       <c r="C30" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E30" t="s">
         <v>21</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G30" t="s">
@@ -1760,13 +1761,13 @@
       <c r="C31" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>21</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G31" t="s">
@@ -1789,13 +1790,13 @@
       <c r="C32" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E32" t="s">
         <v>21</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G32" t="s">
@@ -1818,13 +1819,13 @@
       <c r="C33" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="5" t="s">
         <v>106</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G33" t="s">
@@ -1844,25 +1845,25 @@
       <c r="B34" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1873,25 +1874,25 @@
       <c r="B35" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="5" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1902,25 +1903,25 @@
       <c r="B36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1960,13 +1961,13 @@
       <c r="B38" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -2033,15 +2034,15 @@
       <c r="B41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -2137,25 +2138,25 @@
       <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2166,15 +2167,15 @@
       <c r="B46" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -2183,25 +2184,25 @@
       <c r="B47" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="5" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2280,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="10" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2295,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="10" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2335,7 +2336,7 @@
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2360,7 +2361,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="7"/>
-      <c r="N15" s="8" t="s">
+      <c r="N15" s="10" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2379,27 +2380,27 @@
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="10" t="s">
         <v>139</v>
       </c>
       <c r="J18" s="7"/>
-      <c r="N18" s="8" t="s">
+      <c r="N18" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="O18" s="8" t="s">
+      <c r="O18" s="10" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2419,7 +2420,7 @@
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="10" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2433,7 +2434,7 @@
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>138</v>
       </c>
       <c r="N23" s="7"/>
@@ -2442,10 +2443,10 @@
       <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="10" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2453,7 +2454,7 @@
       <c r="A25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2471,7 +2472,7 @@
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="M28" s="10" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2484,7 +2485,7 @@
       <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="Q30" s="10" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2513,7 +2514,7 @@
       <c r="A35" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2579,7 +2580,7 @@
       <c r="A47" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="10" t="s">
         <v>133</v>
       </c>
     </row>

--- a/Assets/(No) Notes/Felix Inferno.xlsx
+++ b/Assets/(No) Notes/Felix Inferno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stock\Documents\GitHub\felix-inferno\Assets\(No) Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D055451C-D729-4DBD-8B93-9A088B29EFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496AFEBF-D00C-44D5-AF32-290ECBC067EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72B13B88-D491-4DB2-8E71-EA93C3D3E42C}"/>
   </bookViews>
   <sheets>
     <sheet name="Voice lines Felix" sheetId="1" r:id="rId1"/>
@@ -570,7 +570,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -603,8 +603,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1605,13 +1604,13 @@
       <c r="E25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="5" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="I25" s="5"/>
@@ -2281,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2296,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="9" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2336,7 +2335,7 @@
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2361,7 +2360,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="7"/>
-      <c r="N15" s="10" t="s">
+      <c r="N15" s="9" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2381,26 +2380,26 @@
         <v>11</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="9" t="s">
         <v>139</v>
       </c>
       <c r="J18" s="7"/>
-      <c r="N18" s="10" t="s">
+      <c r="N18" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="9" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2420,7 +2419,7 @@
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="9" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2434,7 +2433,7 @@
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>138</v>
       </c>
       <c r="N23" s="7"/>
@@ -2443,10 +2442,10 @@
       <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2454,7 +2453,7 @@
       <c r="A25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2472,7 +2471,7 @@
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="M28" s="10" t="s">
+      <c r="M28" s="9" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2485,7 +2484,7 @@
       <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Q30" s="10" t="s">
+      <c r="Q30" s="9" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2514,7 +2513,7 @@
       <c r="A35" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="9" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2580,7 +2579,7 @@
       <c r="A47" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="9" t="s">
         <v>133</v>
       </c>
     </row>
